--- a/data/trans_dic/IP22D3_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP22D3_R_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,01</t>
+          <t>0,0; 15,77</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2701</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2885</t>
+          <t>0; 2240</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2435</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 2902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 2785</t>
+          <t>0; 2494</t>
         </is>
       </c>
     </row>
